--- a/metadata/plate_metadata/20260415_sci_cep290_48hpf_plate01_well_metadata.xlsx
+++ b/metadata/plate_metadata/20260415_sci_cep290_48hpf_plate01_well_metadata.xlsx
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C3" s="14" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="D3" s="10" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="G3" s="10" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="I8" s="13" t="inlineStr">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>cep290_wt</t>
+          <t>cep290_wildtype</t>
         </is>
       </c>
       <c r="F9" s="11" t="inlineStr">
@@ -2576,6 +2576,18 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
       <c r="H22" s="20" t="n"/>
     </row>
